--- a/GUA/IPPU/B1_Model_Structure.xlsx
+++ b/GUA/IPPU/B1_Model_Structure.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98B981E6-9EC6-4BA2-9A7D-2BB26F270274}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20AAF87E-8109-4F12-A2D0-F2441C484B0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="sets" sheetId="1" r:id="rId1"/>
@@ -13,7 +13,7 @@
     <sheet name="variables" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">sets!$A$1:$L$131</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">sets!$A$1:$L$151</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="385" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="422" uniqueCount="164">
   <si>
     <t>set</t>
   </si>
@@ -383,6 +383,9 @@
     <t>RAW_MAT_CEM</t>
   </si>
   <si>
+    <t>IMP_STOR</t>
+  </si>
+  <si>
     <t>PROD_CLK_TRAD</t>
   </si>
   <si>
@@ -395,64 +398,133 @@
     <t>CEM_PROD</t>
   </si>
   <si>
-    <t>T5CEM_PRODCEM_PROD</t>
-  </si>
-  <si>
-    <t>E5_CEM_PRODCEM_PROD</t>
+    <t>CO2e_IPPU</t>
+  </si>
+  <si>
+    <t>E5INDCEM_PROD</t>
+  </si>
+  <si>
+    <t>T5CEM_PRODIND</t>
+  </si>
+  <si>
+    <t>PARAFFIN</t>
+  </si>
+  <si>
+    <t>E5IPPUPARAFFIN</t>
+  </si>
+  <si>
+    <t>T5PARAFFINIPPU</t>
+  </si>
+  <si>
+    <t>LUBRI_OILS</t>
+  </si>
+  <si>
+    <t>T5LUBRI_OILSIPPU</t>
+  </si>
+  <si>
+    <t>E5IPPULUBRI_OILS</t>
+  </si>
+  <si>
+    <t>REFR_AC_HFC32</t>
+  </si>
+  <si>
+    <t>REFR_AC_HFC125</t>
+  </si>
+  <si>
+    <t>REFR_AC_HFC134a</t>
+  </si>
+  <si>
+    <t>REFR_AC_HFC143a</t>
+  </si>
+  <si>
+    <t>T5REFR_AC_HFC32IPPU</t>
+  </si>
+  <si>
+    <t>T5REFR_AC_HFC125IPPU</t>
+  </si>
+  <si>
+    <t>T5REFR_AC_HFC134aIPPU</t>
+  </si>
+  <si>
+    <t>T5REFR_AC_HFC143aIPPU</t>
+  </si>
+  <si>
+    <t>E5IPPUREFR_AC_HFC32</t>
+  </si>
+  <si>
+    <t>E5IPPUREFR_AC_HFC125</t>
+  </si>
+  <si>
+    <t>E5IPPUREFR_AC_HFC134a</t>
+  </si>
+  <si>
+    <t>E5IPPUREFR_AC_HFC143a</t>
+  </si>
+  <si>
+    <t>PROD_FERRO</t>
+  </si>
+  <si>
+    <t>E5IPPUPROD_FERRO</t>
+  </si>
+  <si>
+    <t>T5PROD_FERROIPPU</t>
   </si>
   <si>
     <t>GUA</t>
   </si>
   <si>
-    <t>PROD_CAL</t>
-  </si>
-  <si>
-    <t>PROD_VID</t>
-  </si>
-  <si>
-    <t>CARBO_PROC</t>
-  </si>
-  <si>
-    <t>PROD_HIER</t>
-  </si>
-  <si>
-    <t>PROD_FERRO</t>
-  </si>
-  <si>
-    <t>LUBRI</t>
-  </si>
-  <si>
-    <t>CERA_PAR</t>
-  </si>
-  <si>
-    <t>REFR_AC</t>
-  </si>
-  <si>
-    <t>CO2e_CEM</t>
-  </si>
-  <si>
-    <t>CO2e_CAL</t>
-  </si>
-  <si>
-    <t>CO2e_VID</t>
-  </si>
-  <si>
-    <t>CO2e_CARBONATO</t>
-  </si>
-  <si>
-    <t>CO2e_HIER</t>
-  </si>
-  <si>
-    <t>CO2e_FERRO</t>
-  </si>
-  <si>
-    <t>CO2e_LUB</t>
-  </si>
-  <si>
-    <t>CO2e_CERAS</t>
-  </si>
-  <si>
-    <t>CO2e_RAC</t>
+    <t>LIME_CAL_PROD</t>
+  </si>
+  <si>
+    <t>LIME_DOL_PROD</t>
+  </si>
+  <si>
+    <t>GLASS_PROD</t>
+  </si>
+  <si>
+    <t>CARBONATE_CERAMICS</t>
+  </si>
+  <si>
+    <t>CARBONATE_ASH</t>
+  </si>
+  <si>
+    <t>IRON_STEEL</t>
+  </si>
+  <si>
+    <t>E5IPPULIME_CAL_PROD</t>
+  </si>
+  <si>
+    <t>T5LIME_CAL_PRODIPPU</t>
+  </si>
+  <si>
+    <t>E5IPPULIME_DOL_PROD</t>
+  </si>
+  <si>
+    <t>T5LIME_DOL_PRODIPPU</t>
+  </si>
+  <si>
+    <t>E5IPPUGLASS_PROD</t>
+  </si>
+  <si>
+    <t>T5GLASS_PRODIPPU</t>
+  </si>
+  <si>
+    <t>E5IPPUCARBONATE_CERAMICS</t>
+  </si>
+  <si>
+    <t>T5CARBONATE_CERAMICSIPPU</t>
+  </si>
+  <si>
+    <t>E5IPPUCARBONATE_ASH</t>
+  </si>
+  <si>
+    <t>T5CARBONATE_ASHIPPU</t>
+  </si>
+  <si>
+    <t>E5IPPUIRON_STEEL</t>
+  </si>
+  <si>
+    <t>T5IRON_STEELIPPU</t>
   </si>
 </sst>
 </file>
@@ -771,20 +843,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L36"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.5546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="21" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="24" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="20.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="7.5703125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.28515625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="21.88671875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="20.44140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="7.5546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.33203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="17.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -822,7 +894,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>22</v>
       </c>
@@ -860,29 +932,29 @@
         <v>31</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>1</v>
       </c>
       <c r="B3">
-        <f t="shared" ref="B3:L3" si="0">+COUNTA(B4:B1048576)</f>
+        <f>+COUNTA(B4:B1048576)</f>
         <v>33</v>
       </c>
       <c r="C3">
         <f>+COUNTA(C4:C1048576)</f>
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="D3">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="D3:L3" si="0">+COUNTA(D4:D1048576)</f>
         <v>1</v>
       </c>
       <c r="E3">
         <f>+COUNTA(E4:E1048576)</f>
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="F3">
-        <f t="shared" si="0"/>
-        <v>9</v>
+        <f>+COUNTA(F4:F1048576)</f>
+        <v>1</v>
       </c>
       <c r="G3">
         <f t="shared" si="0"/>
@@ -909,7 +981,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B4">
         <v>2018</v>
       </c>
@@ -923,16 +995,16 @@
         <v>114</v>
       </c>
       <c r="F4" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="G4">
         <v>1</v>
       </c>
       <c r="H4" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B5">
         <v>2019</v>
       </c>
@@ -942,11 +1014,8 @@
       <c r="E5" t="s">
         <v>115</v>
       </c>
-      <c r="F5" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B6">
         <v>2020</v>
       </c>
@@ -954,212 +1023,326 @@
         <v>116</v>
       </c>
       <c r="E6" t="s">
-        <v>118</v>
-      </c>
-      <c r="F6" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B7">
         <v>2021</v>
       </c>
       <c r="C7" t="s">
-        <v>117</v>
+        <v>146</v>
       </c>
       <c r="E7" t="s">
-        <v>119</v>
-      </c>
-      <c r="F7" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B8">
         <v>2022</v>
       </c>
       <c r="C8" t="s">
-        <v>120</v>
+        <v>147</v>
       </c>
       <c r="E8" t="s">
-        <v>121</v>
-      </c>
-      <c r="F8" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B9">
         <v>2023</v>
       </c>
       <c r="C9" t="s">
-        <v>123</v>
-      </c>
-      <c r="F9" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+        <v>148</v>
+      </c>
+      <c r="E9" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B10">
         <v>2024</v>
       </c>
       <c r="C10" t="s">
-        <v>124</v>
-      </c>
-      <c r="F10" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+        <v>149</v>
+      </c>
+      <c r="E10" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B11">
         <v>2025</v>
       </c>
       <c r="C11" t="s">
-        <v>125</v>
-      </c>
-      <c r="F11" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+        <v>150</v>
+      </c>
+      <c r="E11" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B12">
         <v>2026</v>
       </c>
       <c r="C12" t="s">
-        <v>126</v>
-      </c>
-      <c r="F12" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+        <v>151</v>
+      </c>
+      <c r="E12" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B13">
         <v>2027</v>
       </c>
       <c r="C13" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+        <v>142</v>
+      </c>
+      <c r="E13" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B14">
         <v>2028</v>
       </c>
       <c r="C14" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+        <v>127</v>
+      </c>
+      <c r="E14" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B15">
         <v>2029</v>
       </c>
       <c r="C15" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+        <v>124</v>
+      </c>
+      <c r="E15" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B16">
         <v>2030</v>
       </c>
       <c r="C16" t="s">
         <v>130</v>
       </c>
-    </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="E16" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="17" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B17">
         <v>2031</v>
       </c>
-    </row>
-    <row r="18" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="C17" t="s">
+        <v>131</v>
+      </c>
+      <c r="E17" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="18" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B18">
         <v>2032</v>
       </c>
-    </row>
-    <row r="19" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="C18" t="s">
+        <v>132</v>
+      </c>
+      <c r="E18" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="19" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B19">
         <v>2033</v>
       </c>
-    </row>
-    <row r="20" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="C19" t="s">
+        <v>133</v>
+      </c>
+      <c r="E19" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="20" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B20">
         <v>2034</v>
       </c>
-    </row>
-    <row r="21" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="C20" t="s">
+        <v>117</v>
+      </c>
+      <c r="E20" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="21" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B21">
         <v>2035</v>
       </c>
-    </row>
-    <row r="22" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="C21" t="s">
+        <v>118</v>
+      </c>
+      <c r="E21" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="22" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B22">
         <v>2036</v>
       </c>
-    </row>
-    <row r="23" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="C22" t="s">
+        <v>123</v>
+      </c>
+      <c r="E22" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="23" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B23">
         <v>2037</v>
       </c>
-    </row>
-    <row r="24" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="C23" t="s">
+        <v>153</v>
+      </c>
+      <c r="E23" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="24" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B24">
         <v>2038</v>
       </c>
-    </row>
-    <row r="25" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="C24" t="s">
+        <v>155</v>
+      </c>
+      <c r="E24" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="25" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B25">
         <v>2039</v>
       </c>
-    </row>
-    <row r="26" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="C25" t="s">
+        <v>157</v>
+      </c>
+      <c r="E25" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="26" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B26">
         <v>2040</v>
       </c>
-    </row>
-    <row r="27" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="C26" t="s">
+        <v>159</v>
+      </c>
+      <c r="E26" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="27" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B27">
         <v>2041</v>
       </c>
-    </row>
-    <row r="28" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="C27" t="s">
+        <v>161</v>
+      </c>
+      <c r="E27" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="28" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B28">
         <v>2042</v>
       </c>
-    </row>
-    <row r="29" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="C28" t="s">
+        <v>163</v>
+      </c>
+      <c r="E28" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="29" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B29">
         <v>2043</v>
       </c>
-    </row>
-    <row r="30" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="C29" t="s">
+        <v>144</v>
+      </c>
+      <c r="E29" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="30" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B30">
         <v>2044</v>
       </c>
-    </row>
-    <row r="31" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="C30" t="s">
+        <v>128</v>
+      </c>
+      <c r="E30" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="31" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B31">
         <v>2045</v>
       </c>
-    </row>
-    <row r="32" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="C31" t="s">
+        <v>126</v>
+      </c>
+      <c r="E31" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="32" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B32">
         <v>2046</v>
       </c>
-    </row>
-    <row r="33" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="C32" t="s">
+        <v>134</v>
+      </c>
+      <c r="E32" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="33" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B33">
         <v>2047</v>
       </c>
-    </row>
-    <row r="34" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="C33" t="s">
+        <v>135</v>
+      </c>
+      <c r="E33" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="34" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B34">
         <v>2048</v>
       </c>
-    </row>
-    <row r="35" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="C34" t="s">
+        <v>136</v>
+      </c>
+      <c r="E34" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="35" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B35">
         <v>2049</v>
       </c>
-    </row>
-    <row r="36" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="C35" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="36" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B36">
         <v>2050</v>
       </c>
@@ -1172,39 +1355,39 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D8A1DB5-AB21-4E2D-94E4-FE18AAF65A94}">
   <dimension ref="A1:AE8"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.140625" customWidth="1"/>
-    <col min="3" max="3" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="20.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="20.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="19.7109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.7109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="15.7109375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="17.28515625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="21.7109375" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="21.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.109375" customWidth="1"/>
+    <col min="3" max="3" width="11.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="19.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.88671875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.109375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="21.6640625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="21.109375" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="31" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="30.5703125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="35.7109375" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="35.85546875" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="40.7109375" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="40.7109375" customWidth="1"/>
-    <col min="25" max="25" width="18.5703125" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="20.5703125" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="18.7109375" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="13.85546875" customWidth="1"/>
+    <col min="20" max="20" width="30.5546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="35.6640625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="35.88671875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="40.6640625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="40.6640625" customWidth="1"/>
+    <col min="25" max="25" width="18.5546875" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="20.5546875" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="18.6640625" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="13.88671875" customWidth="1"/>
     <col min="31" max="31" width="15" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>14</v>
       </c>
@@ -1233,7 +1416,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -1328,7 +1511,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -1453,7 +1636,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
         <v>24</v>
       </c>
@@ -1545,7 +1728,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
         <v>20</v>
       </c>
@@ -1631,7 +1814,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.3">
       <c r="E6" t="s">
         <v>20</v>
       </c>
@@ -1696,7 +1879,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.3">
       <c r="F7" t="s">
         <v>20</v>
       </c>
@@ -1716,7 +1899,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.3">
       <c r="L8" t="s">
         <v>20</v>
       </c>
@@ -1736,43 +1919,43 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A61DBA02-50DA-45DC-88DC-E3B8D7B75762}">
   <dimension ref="A1:AR9"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="27.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="22.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="27.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="22.6640625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="18" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="17.28515625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="26.5703125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="33.42578125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="31.5703125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="34.42578125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="27.42578125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="21.5703125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="27.28515625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="15.7109375" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="28.42578125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="21.5703125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="21.28515625" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="15.5703125" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="15.85546875" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="25.28515625" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="26.5546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="33.44140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="31.5546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="34.44140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="27.44140625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="21.5546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="27.33203125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="28.44140625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="21.5546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="21.33203125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="15.5546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="15.88671875" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="25.33203125" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="11.6640625" bestFit="1" customWidth="1"/>
     <col min="27" max="27" width="21" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="22.140625" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="25.28515625" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="22.7109375" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="29.85546875" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="22.109375" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="25.33203125" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="22.6640625" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="29.88671875" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="18.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>14</v>
       </c>
@@ -1792,7 +1975,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="2" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>55</v>
       </c>
@@ -1926,7 +2109,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="3" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -2103,7 +2286,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:44" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
         <v>19</v>
       </c>
@@ -2234,7 +2417,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:44" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
         <v>24</v>
       </c>
@@ -2365,7 +2548,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="6" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:44" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
         <v>25</v>
       </c>
@@ -2478,7 +2661,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:44" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
         <v>20</v>
       </c>
@@ -2534,7 +2717,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:44" x14ac:dyDescent="0.3">
       <c r="H8" t="s">
         <v>20</v>
       </c>
@@ -2560,7 +2743,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:44" x14ac:dyDescent="0.3">
       <c r="M9" t="s">
         <v>20</v>
       </c>
@@ -2574,6 +2757,16 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="a1fcbaaf-06d9-47c4-b3a2-beefbc45d784">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -2582,7 +2775,7 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101000360DE9767CDF0449BF75EAB371D3CB7" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="75cb9a07855af6ac97bd432464ca7c04">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="a1fcbaaf-06d9-47c4-b3a2-beefbc45d784" xmlns:ns3="081a93ea-d517-42a5-a2b7-457060aa7471" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d1676634304aab9936f6a5a5f53c7423" ns2:_="" ns3:_="">
     <xsd:import namespace="a1fcbaaf-06d9-47c4-b3a2-beefbc45d784"/>
@@ -2805,28 +2998,42 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="a1fcbaaf-06d9-47c4-b3a2-beefbc45d784">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{94B79A15-FCC6-40B1-BEF8-F88BEF3CE214}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="0d55314f-45f1-40c9-9fce-63556e193d03"/>
+    <ds:schemaRef ds:uri="48eed89a-7418-4977-ae3a-838f0fac8ec5"/>
+    <ds:schemaRef ds:uri="416d42ac-85ec-40c4-8054-6c816fd4b6a7"/>
+    <ds:schemaRef ds:uri="a1fcbaaf-06d9-47c4-b3a2-beefbc45d784"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EB967245-AB76-42EE-9F96-1A9CAD76BA5D}">
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2E67016B-2BB4-478C-AF15-1A9FF8562EBE}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{422502FE-2DDC-4452-BC51-F6C756E54471}"/>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E0D0014F-F87F-42E6-9402-186A47C0B8C2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EF2487F5-2D0F-43FD-AD29-5F6913A067A4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="a1fcbaaf-06d9-47c4-b3a2-beefbc45d784"/>
+    <ds:schemaRef ds:uri="081a93ea-d517-42a5-a2b7-457060aa7471"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>